--- a/public/templates/student-template.xlsx
+++ b/public/templates/student-template.xlsx
@@ -437,7 +437,7 @@
         <v>OO중학교</v>
       </c>
       <c r="E2" t="str">
-        <v>중1</v>
+        <v>2학년</v>
       </c>
     </row>
   </sheetData>
